--- a/pipeline/tests/fixtures/wb_pink_sheet/CMO-Historical-Data-Monthly.xlsx
+++ b/pipeline/tests/fixtures/wb_pink_sheet/CMO-Historical-Data-Monthly.xlsx
@@ -2703,7 +2703,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Updated on September 02, 2026</t>
+          <t>Updated on October 02, 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -17657,11 +17657,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>World Bank Commodity Price Data (The Pink Sheet)</t>
-        </is>
-      </c>
+      <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -17728,7 +17724,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Updated on September 02, 2026</t>
+          <t>Updated on October 02, 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -21666,7 +21662,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palm oil (Malaysia), from February 2025, Crude, DAP; November 2024-January 2025, 5% Bulk, CIF North West Europe; January 2021 to October 2024, RBD, FOB Malaysia Ports; December 2001 to December 2020, RBD, CIF Rotterdam; previously Malaysia 5%,  c.i.f. N.W. Europe, bulk, nearest forward .</t>
+          <t>Palm oil (Malaysia), from January 2026, RBD, average export price FOB;February-December 2025, Crude, DAP; November 2024-January 2025, 5% Bulk, CIF North West Europe; January 2021 to October 2024, RBD, FOB Malaysia Ports; December 2001 to December 2020, RBD, CIF Rotterdam; previously Malaysia 5%,  c.i.f. N.W. Europe, bulk, nearest forward .</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
